--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0012.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0012.xlsx
@@ -14094,7 +14094,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>{PlayerName}, cậu thật tuyệt vời! Ngay cả câu đố khó như vậy cậu cũng biết答案!</t>
+          <t>{PlayerName}, cậu thật tuyệt vời! Ngay cả câu đố khó như vậy cậu cũng biết đáp án!</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>{PlayerName}, cậu thật tuyệt vời! Ngay cả câu đố khó như vậy cậu cũng biết答案!</t>
+          <t>{PlayerName}, cậu thật tuyệt vời! Ngay cả câu đố khó như vậy cậu cũng biết đáp án!</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>{PlayerName}, cậu thật tuyệt vời! Ngay cả câu đố khó như vậy cậu cũng biết答案!</t>
+          <t>{PlayerName}, cậu thật tuyệt vời! Ngay cả câu đố khó như vậy cậu cũng biết đáp án!</t>
         </is>
       </c>
     </row>
@@ -17019,7 +17019,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>{PlayerName}, cậu thật tuyệt vời! Ngay cả câu đố khó như vậy cậu cũng biết答案!</t>
+          <t>{PlayerName}, cậu thật tuyệt vời! Ngay cả câu đố khó như vậy cậu cũng biết đáp án!</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>{PlayerName}, cậu thật tuyệt vời! Ngay cả câu đố khó như vậy cậu cũng biết答案!</t>
+          <t>{PlayerName}, cậu thật tuyệt vời! Ngay cả câu đố khó như vậy cậu cũng biết đáp án!</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>{PlayerName}, cậu thật tuyệt vời! Ngay cả câu đố khó như vậy cậu cũng biết答案!</t>
+          <t>{PlayerName}, cậu thật tuyệt vời! Ngay cả câu đố khó như vậy cậu cũng biết đáp án!</t>
         </is>
       </c>
     </row>
